--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_290_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_290_R29.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6225</v>
+        <v>6.0003</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8407</v>
+        <v>4.1513</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7818</v>
+        <v>1.849</v>
       </c>
       <c r="G2" t="n">
         <v>5.6038</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5175</v>
+        <v>-0.1397</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5149</v>
+        <v>-0.2043</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0026</v>
+        <v>0.0646</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3381</v>
+        <v>5.0087</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3131</v>
+        <v>2.8738</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0249</v>
+        <v>2.1349</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6049</v>
+        <v>5.685</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6374</v>
+        <v>1.0073</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9675</v>
+        <v>4.6776</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0362</v>
+        <v>4.6703</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1161</v>
+        <v>0.6218</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9201</v>
+        <v>4.0485</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5686</v>
+        <v>1.0146</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5213</v>
+        <v>0.3856</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0474</v>
+        <v>0.6291</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1971</v>
+        <v>-0.2124</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1325</v>
+        <v>-0.4048</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0646</v>
+        <v>0.1924</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8907</v>
+        <v>4.5625</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7559</v>
+        <v>1.3695</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1349</v>
+        <v>3.193</v>
       </c>
       <c r="G4" t="n">
-        <v>5.685</v>
+        <v>3.6049</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0073</v>
+        <v>1.6374</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6776</v>
+        <v>1.9675</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6703</v>
+        <v>2.0362</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6218</v>
+        <v>1.1161</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0485</v>
+        <v>0.9201</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0146</v>
+        <v>1.5686</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3856</v>
+        <v>0.5213</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6291</v>
+        <v>1.0474</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3304</v>
+        <v>0.4215</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5228</v>
+        <v>0.1889</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1924</v>
+        <v>0.2326</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8326</v>
+        <v>3.0013</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3459</v>
+        <v>1.5818</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4867</v>
+        <v>1.4195</v>
       </c>
       <c r="G5" t="n">
         <v>4.0638</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.159</v>
+        <v>0.0097</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2812</v>
+        <v>0.2139</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7623</v>
+        <v>2.1004</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6268</v>
+        <v>0.0809</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3892</v>
+        <v>2.0195</v>
       </c>
       <c r="G6" t="n">
         <v>0.6056</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0031</v>
+        <v>0.335</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5149</v>
+        <v>0.1928</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5118</v>
+        <v>0.1421</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2583</v>
+        <v>1.8377</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1371</v>
+        <v>1.4477</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1212</v>
+        <v>0.3901</v>
       </c>
       <c r="G7" t="n">
         <v>3.54</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1942</v>
+        <v>0.3853</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3541</v>
+        <v>0.6647</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5482</v>
+        <v>-0.2794</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1255</v>
+        <v>1.2942</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4495</v>
+        <v>1.6854</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3241</v>
+        <v>-0.3913</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1927</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.246</v>
+        <v>0.4147</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2715</v>
+        <v>0.5074</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0255</v>
+        <v>-0.0927</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2284</v>
+        <v>0.1362</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1661</v>
+        <v>0.8407</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0623</v>
+        <v>-0.7046</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1331</v>
+        <v>-0.0648</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3206</v>
+        <v>-0.2689</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1874</v>
+        <v>0.2041</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4174</v>
+        <v>0.4107</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2451</v>
+        <v>-0.215</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6625</v>
+        <v>0.6257</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5505</v>
+        <v>-0.4755</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0755</v>
+        <v>-0.0539</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4751</v>
+        <v>-0.4216</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7532</v>
+        <v>-0.5671</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0682</v>
+        <v>-0.1061</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.315</v>
+        <v>-0.461</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1573</v>
+        <v>-0.2926</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6481</v>
+        <v>0.3058</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8054</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0648</v>
+        <v>-0.1622</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2689</v>
+        <v>0.7648</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2041</v>
+        <v>-0.927</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4107</v>
+        <v>0.4418</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.215</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6257</v>
+        <v>-0.3984</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4755</v>
+        <v>-0.604</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0539</v>
+        <v>-0.0755</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4216</v>
+        <v>-0.5286</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8606</v>
+        <v>0.2614</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>0.4876</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5619</v>
+        <v>-0.2262</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3598</v>
+        <v>-0.5979</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3058</v>
+        <v>-0.8955</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6655</v>
+        <v>0.2975</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1622</v>
+        <v>-0.1331</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7648</v>
+        <v>-0.3206</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.927</v>
+        <v>0.1874</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4418</v>
+        <v>0.4174</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8401999999999999</v>
+        <v>-0.2451</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3984</v>
+        <v>0.6625</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.604</v>
+        <v>-0.5505</v>
       </c>
       <c r="N11" t="n">
         <v>-0.0755</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5286</v>
+        <v>-0.4751</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1942</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4876</v>
+        <v>1.0067</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2934</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.7387</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.366</v>
+        <v>-0.9374</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.1987</v>
       </c>
       <c r="G12" t="n">
         <v>0.2216</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2078</v>
+        <v>0.1994</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3655</v>
+        <v>0.063</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5733</v>
+        <v>0.1364</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7201</v>
+        <v>-1.8477</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8475</v>
+        <v>-2.0087</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1274</v>
+        <v>0.161</v>
       </c>
       <c r="G13" t="n">
         <v>0.6518</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2544</v>
+        <v>0.1267</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2715</v>
+        <v>0.1103</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0171</v>
+        <v>0.0165</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4665</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.0909</v>
+        <v>20.4644</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1219</v>
+        <v>10.4953</v>
       </c>
       <c r="F14" t="n">
         <v>9.968999999999999</v>
@@ -1513,7 +1513,7 @@
         <v>23.4237</v>
       </c>
       <c r="H14" t="n">
-        <v>9.220399999999998</v>
+        <v>9.2204</v>
       </c>
       <c r="I14" t="n">
         <v>14.2031</v>
@@ -1522,13 +1522,13 @@
         <v>20.7106</v>
       </c>
       <c r="K14" t="n">
-        <v>7.260800000000001</v>
+        <v>7.2608</v>
       </c>
       <c r="L14" t="n">
         <v>13.4495</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7134</v>
+        <v>2.713400000000001</v>
       </c>
       <c r="N14" t="n">
         <v>1.9595</v>
@@ -1546,13 +1546,13 @@
         <v>12.7575</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7879</v>
+        <v>2.1614</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9284</v>
+        <v>2.3019</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1403999999999999</v>
+        <v>-0.1405000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.6779000000000002</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1305</v>
+        <v>2.0772</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6559</v>
+        <v>2.978</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5253</v>
+        <v>-0.9008</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.0323</v>
+        <v>-0.1165</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1155</v>
+        <v>1.2052</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9167</v>
+        <v>-1.3217</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.3668</v>
+        <v>3.0535</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.0293</v>
+        <v>1.9529</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6625</v>
+        <v>1.1006</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6655</v>
+        <v>-3.17</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0862</v>
+        <v>-0.7477</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5792</v>
+        <v>-2.4223</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4669</v>
+        <v>-0.0382</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1102</v>
+        <v>0.0121</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3567</v>
+        <v>-0.0503</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
         <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.3545</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1524</v>
+        <v>0.7134</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5178</v>
+        <v>-0.3589</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1165</v>
+        <v>-0.057</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2052</v>
+        <v>-0.3481</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3217</v>
+        <v>0.2912</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0535</v>
+        <v>1.523</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9529</v>
+        <v>0.8605</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1006</v>
+        <v>0.6625</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.17</v>
+        <v>-1.58</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7477</v>
+        <v>-1.2087</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4223</v>
+        <v>-0.3713</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4809</v>
+        <v>-0.6761</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8136</v>
+        <v>-0.8096</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6673</v>
+        <v>0.1336</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5194</v>
+        <v>0.1161</v>
       </c>
       <c r="E17" t="n">
-        <v>1.724</v>
+        <v>0.2359</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2046</v>
+        <v>-0.1198</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3375</v>
+        <v>-2.4239</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5162</v>
+        <v>-0.0818</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8537</v>
+        <v>-2.3421</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4421</v>
+        <v>-0.4406</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8739</v>
+        <v>0.1617</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4317</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7796</v>
+        <v>-1.9833</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3577</v>
+        <v>-0.2435</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.422</v>
+        <v>-1.7398</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>2.7834</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>2.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>1.393</v>
+        <v>0.4345</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2819</v>
+        <v>0.6765</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1111</v>
+        <v>-0.242</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1605</v>
+        <v>-0.1039</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2359</v>
+        <v>1.1342</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-1.2382</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4239</v>
+        <v>-1.3375</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0818</v>
+        <v>0.5162</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3421</v>
+        <v>-1.8537</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4406</v>
+        <v>0.4421</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1617</v>
+        <v>0.8739</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.4317</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9833</v>
+        <v>-1.7796</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2435</v>
+        <v>-0.3577</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7398</v>
+        <v>-1.422</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7834</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7834</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4788</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6765</v>
+        <v>0.6921</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1977</v>
+        <v>0.0775</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1503</v>
+        <v>-0.1383</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4775</v>
+        <v>-0.3533</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6278</v>
+        <v>0.2149</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.057</v>
+        <v>-0.7074</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3481</v>
+        <v>-1.0923</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2912</v>
+        <v>0.3849</v>
       </c>
       <c r="J19" t="n">
-        <v>1.523</v>
+        <v>0.1576</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8605</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6625</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.58</v>
+        <v>-0.8651</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2087</v>
+        <v>-1.1763</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3713</v>
+        <v>0.3113</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1808</v>
+        <v>-0.8226</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0455</v>
+        <v>-0.5109</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1353</v>
+        <v>-0.3117</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4979</v>
+        <v>-1.2729</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09130000000000001</v>
+        <v>-0.5697</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7074</v>
+        <v>-3.0323</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0923</v>
+        <v>-2.1155</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3849</v>
+        <v>-0.9167</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1576</v>
+        <v>-1.3668</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08400000000000001</v>
+        <v>-2.0293</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>0.6625</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8651</v>
+        <v>-1.6655</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1763</v>
+        <v>-0.0862</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3113</v>
+        <v>-1.5792</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1822</v>
+        <v>1.0635</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7468</v>
+        <v>0.7512</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4353</v>
+        <v>0.3123</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5503</v>
+        <v>-2.8534</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5536</v>
+        <v>-0.8459</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9967</v>
+        <v>-2.0075</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8918</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3544</v>
+        <v>-0.6574</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2617</v>
+        <v>-0.554</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0927</v>
+        <v>-0.1034</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6544</v>
+        <v>-3.818</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9374</v>
+        <v>-4.5836</v>
       </c>
       <c r="F22" t="n">
-        <v>0.283</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2154</v>
@@ -2170,13 +2170,13 @@
         <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0319</v>
+        <v>-0.1955</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.55</v>
+        <v>-0.1962</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4819</v>
+        <v>0.0007</v>
       </c>
       <c r="V22" t="n">
         <v>1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1544</v>
+        <v>-6.143</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7797</v>
+        <v>-4.0156</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3747</v>
+        <v>-2.1274</v>
       </c>
       <c r="G23" t="n">
         <v>-6.6715</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2697</v>
+        <v>0.2812</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9085</v>
+        <v>0.6726</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6387</v>
+        <v>-0.3914</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6083</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.5285</v>
+        <v>-6.7364</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4268</v>
+        <v>-5.6012</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1017</v>
+        <v>-1.1353</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9705</v>
@@ -2326,13 +2326,13 @@
         <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1663</v>
+        <v>-0.3743</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4189</v>
+        <v>-0.5933</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2526</v>
+        <v>0.219</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.0908</v>
+        <v>-18.5181</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.041</v>
+        <v>-11.0412</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.0497</v>
+        <v>-7.477099999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-23.4238</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.2204</v>
+        <v>-9.220399999999998</v>
       </c>
       <c r="I25" t="n">
         <v>-14.2031</v>
@@ -2389,13 +2389,13 @@
         <v>-20.7106</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.261</v>
+        <v>-7.260999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-13.4495</v>
       </c>
       <c r="P25" t="n">
-        <v>5.798899999999999</v>
+        <v>5.798900000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.7575</v>
@@ -2404,13 +2404,13 @@
         <v>18.5561</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7881</v>
+        <v>-0.2152</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1405999999999998</v>
+        <v>0.1404999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.9285</v>
+        <v>-0.3557</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6778999999999999</v>
